--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="46">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>40.42%</t>
+    <t>57.84%</t>
   </si>
   <si>
     <t>Extra Suite</t>
@@ -109,7 +109,7 @@
     <t>Parrilladas</t>
   </si>
   <si>
-    <t>88.10%</t>
+    <t>88.89%</t>
   </si>
   <si>
     <t>Primer Nivel</t>
@@ -121,34 +121,34 @@
     <t>Suites Primer Nivel</t>
   </si>
   <si>
+    <t>66.67%</t>
+  </si>
+  <si>
+    <t>53.87%</t>
+  </si>
+  <si>
     <t>65.38%</t>
   </si>
   <si>
-    <t>66.67%</t>
-  </si>
-  <si>
-    <t>53.87%</t>
-  </si>
-  <si>
     <t>Suites Segundo Nivel</t>
   </si>
   <si>
+    <t>59.57%</t>
+  </si>
+  <si>
     <t>58.02%</t>
   </si>
   <si>
-    <t>59.57%</t>
-  </si>
-  <si>
     <t>Tercer Nivel</t>
   </si>
   <si>
-    <t>28.87%</t>
+    <t>45.87%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>67.57%</t>
+    <t>74.93%</t>
   </si>
 </sst>
 </file>
@@ -661,10 +661,10 @@
         <v>4198</v>
       </c>
       <c r="C6" s="6">
-        <v>1039</v>
+        <v>1480</v>
       </c>
       <c r="D6" s="6">
-        <v>629</v>
+        <v>874</v>
       </c>
       <c r="E6" s="6">
         <v>11</v>
@@ -693,17 +693,17 @@
       <c r="M6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>22</v>
+      <c r="N6" s="6">
+        <v>50</v>
       </c>
       <c r="O6" s="6">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="P6" s="6">
-        <v>1697</v>
+        <v>2428</v>
       </c>
       <c r="Q6" s="6">
-        <v>2501</v>
+        <v>1770</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -826,29 +826,29 @@
         <v>28</v>
       </c>
       <c r="B9" s="6">
-        <v>189</v>
-      </c>
-      <c r="C9" s="6">
-        <v>31</v>
-      </c>
-      <c r="D9" s="6">
-        <v>29</v>
-      </c>
-      <c r="E9" s="6">
+        <v>265</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="6">
+        <v>158</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="6">
         <v>24</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="6">
-        <v>8</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="6">
-        <v>12</v>
-      </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
       </c>
@@ -862,13 +862,13 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>85</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>22</v>
+        <v>81</v>
+      </c>
+      <c r="O9" s="6">
+        <v>2</v>
       </c>
       <c r="P9" s="6">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>22</v>
@@ -885,7 +885,7 @@
         <v>186</v>
       </c>
       <c r="C10" s="6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6">
         <v>35</v>
@@ -918,7 +918,7 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
@@ -938,28 +938,28 @@
         <v>28</v>
       </c>
       <c r="B11" s="6">
-        <v>265</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
+        <v>189</v>
+      </c>
+      <c r="C11" s="6">
+        <v>47</v>
+      </c>
+      <c r="D11" s="6">
+        <v>29</v>
+      </c>
+      <c r="E11" s="6">
+        <v>24</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -974,13 +974,13 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>83</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>22</v>
+        <v>64</v>
+      </c>
+      <c r="O11" s="6">
+        <v>2</v>
       </c>
       <c r="P11" s="6">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>22</v>
@@ -1050,13 +1050,13 @@
         <v>30</v>
       </c>
       <c r="B13" s="6">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C13" s="6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E13" s="6">
         <v>36</v>
@@ -1064,8 +1064,8 @@
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
+      <c r="G13" s="6">
+        <v>11</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
@@ -1086,13 +1086,13 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>22</v>
@@ -1106,13 +1106,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="6">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="C14" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D14" s="6">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E14" s="6">
         <v>36</v>
@@ -1120,8 +1120,8 @@
       <c r="F14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="6">
-        <v>11</v>
+      <c r="G14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>22</v>
@@ -1142,13 +1142,13 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>22</v>
@@ -1198,16 +1198,16 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="Q15" s="6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>32</v>
@@ -1221,10 +1221,10 @@
         <v>2774</v>
       </c>
       <c r="C16" s="6">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="D16" s="6">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="E16" s="6">
         <v>352</v>
@@ -1233,7 +1233,7 @@
         <v>22</v>
       </c>
       <c r="G16" s="6">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>22</v>
@@ -1254,7 +1254,7 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
@@ -1277,10 +1277,10 @@
         <v>1326</v>
       </c>
       <c r="C17" s="6">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D17" s="6">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E17" s="6">
         <v>153</v>
@@ -1310,10 +1310,10 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>248</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>22</v>
+        <v>241</v>
+      </c>
+      <c r="O17" s="6">
+        <v>1</v>
       </c>
       <c r="P17" s="6">
         <v>1326</v>
@@ -1333,13 +1333,13 @@
         <v>2691</v>
       </c>
       <c r="C18" s="6">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="D18" s="6">
-        <v>977</v>
+        <v>994</v>
       </c>
       <c r="E18" s="6">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1366,7 +1366,7 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>437</v>
+        <v>391</v>
       </c>
       <c r="O18" s="6">
         <v>1</v>
@@ -1386,28 +1386,28 @@
         <v>34</v>
       </c>
       <c r="B19" s="6">
-        <v>1900</v>
-      </c>
-      <c r="C19" s="6">
-        <v>736</v>
+        <v>390</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D19" s="6">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="E19" s="6">
-        <v>305</v>
+        <v>38</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>22</v>
+      <c r="G19" s="6">
+        <v>43</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="6">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1422,13 +1422,13 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>1900</v>
+        <v>390</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>22</v>
@@ -1442,28 +1442,28 @@
         <v>34</v>
       </c>
       <c r="B20" s="6">
-        <v>390</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>22</v>
+        <v>1900</v>
+      </c>
+      <c r="C20" s="6">
+        <v>736</v>
       </c>
       <c r="D20" s="6">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E20" s="6">
-        <v>32</v>
+        <v>305</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="6">
-        <v>43</v>
+      <c r="G20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>22</v>
@@ -1478,13 +1478,13 @@
         <v>22</v>
       </c>
       <c r="N20" s="6">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>390</v>
+        <v>1900</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>22</v>
@@ -1498,7 +1498,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="6">
-        <v>312</v>
+        <v>216</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>22</v>
@@ -1506,20 +1506,20 @@
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="6">
-        <v>12</v>
+      <c r="E21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="6">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>22</v>
@@ -1534,16 +1534,16 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="Q21" s="6">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>36</v>
@@ -1554,7 +1554,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="6">
-        <v>216</v>
+        <v>336</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>22</v>
@@ -1562,20 +1562,20 @@
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>22</v>
+      <c r="E22" s="6">
+        <v>12</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="6">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="6">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>22</v>
@@ -1590,16 +1590,16 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="Q22" s="6">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>37</v>
@@ -1610,7 +1610,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="6">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>22</v>
@@ -1625,13 +1625,13 @@
         <v>22</v>
       </c>
       <c r="G23" s="6">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="6">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>22</v>
@@ -1646,16 +1646,16 @@
         <v>22</v>
       </c>
       <c r="N23" s="6">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="Q23" s="6">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>38</v>
@@ -1666,7 +1666,7 @@
         <v>39</v>
       </c>
       <c r="B24" s="6">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>22</v>
@@ -1675,19 +1675,19 @@
         <v>22</v>
       </c>
       <c r="E24" s="6">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="6">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>22</v>
@@ -1702,19 +1702,19 @@
         <v>22</v>
       </c>
       <c r="N24" s="6">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P24" s="6">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="Q24" s="6">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -1770,7 +1770,7 @@
         <v>110</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -1778,7 +1778,7 @@
         <v>39</v>
       </c>
       <c r="B26" s="6">
-        <v>324</v>
+        <v>264</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>22</v>
@@ -1787,19 +1787,19 @@
         <v>22</v>
       </c>
       <c r="E26" s="6">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="6">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I26" s="6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>22</v>
@@ -1814,19 +1814,19 @@
         <v>22</v>
       </c>
       <c r="N26" s="6">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="Q26" s="6">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -1837,10 +1837,10 @@
         <v>5441</v>
       </c>
       <c r="C27" s="6">
-        <v>1563</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>22</v>
+        <v>2219</v>
+      </c>
+      <c r="D27" s="6">
+        <v>217</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>22</v>
@@ -1869,17 +1869,17 @@
       <c r="M27" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N27" s="6" t="s">
-        <v>22</v>
+      <c r="N27" s="6">
+        <v>50</v>
       </c>
       <c r="O27" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P27" s="6">
-        <v>1571</v>
+        <v>2496</v>
       </c>
       <c r="Q27" s="6">
-        <v>3870</v>
+        <v>2945</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>43</v>

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="46">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>57.84%</t>
+    <t>69.84%</t>
   </si>
   <si>
     <t>Extra Suite</t>
@@ -109,7 +109,7 @@
     <t>Parrilladas</t>
   </si>
   <si>
-    <t>88.89%</t>
+    <t>94.44%</t>
   </si>
   <si>
     <t>Primer Nivel</t>
@@ -121,12 +121,12 @@
     <t>Suites Primer Nivel</t>
   </si>
   <si>
+    <t>53.87%</t>
+  </si>
+  <si>
     <t>66.67%</t>
   </si>
   <si>
-    <t>53.87%</t>
-  </si>
-  <si>
     <t>65.38%</t>
   </si>
   <si>
@@ -142,13 +142,13 @@
     <t>Tercer Nivel</t>
   </si>
   <si>
-    <t>45.87%</t>
+    <t>54.82%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>74.93%</t>
+    <t>79.47%</t>
   </si>
 </sst>
 </file>
@@ -661,10 +661,10 @@
         <v>4198</v>
       </c>
       <c r="C6" s="6">
-        <v>1480</v>
+        <v>1795</v>
       </c>
       <c r="D6" s="6">
-        <v>874</v>
+        <v>1035</v>
       </c>
       <c r="E6" s="6">
         <v>11</v>
@@ -697,13 +697,13 @@
         <v>50</v>
       </c>
       <c r="O6" s="6">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="P6" s="6">
-        <v>2428</v>
+        <v>2932</v>
       </c>
       <c r="Q6" s="6">
-        <v>1770</v>
+        <v>1266</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -826,28 +826,28 @@
         <v>28</v>
       </c>
       <c r="B9" s="6">
-        <v>265</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
+        <v>189</v>
+      </c>
+      <c r="C9" s="6">
+        <v>49</v>
+      </c>
+      <c r="D9" s="6">
+        <v>29</v>
+      </c>
+      <c r="E9" s="6">
+        <v>30</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="6">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -862,13 +862,13 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>81</v>
-      </c>
-      <c r="O9" s="6">
-        <v>2</v>
+        <v>58</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>22</v>
@@ -882,28 +882,28 @@
         <v>28</v>
       </c>
       <c r="B10" s="6">
-        <v>186</v>
+        <v>265</v>
       </c>
       <c r="C10" s="6">
-        <v>17</v>
-      </c>
-      <c r="D10" s="6">
-        <v>35</v>
-      </c>
-      <c r="E10" s="6">
-        <v>36</v>
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>22</v>
+      <c r="I10" s="6">
+        <v>24</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -918,13 +918,13 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>186</v>
+        <v>265</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>22</v>
@@ -938,28 +938,28 @@
         <v>28</v>
       </c>
       <c r="B11" s="6">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C11" s="6">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D11" s="6">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E11" s="6">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6">
-        <v>15</v>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -974,13 +974,13 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>64</v>
-      </c>
-      <c r="O11" s="6">
-        <v>2</v>
+        <v>78</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>22</v>
@@ -994,28 +994,28 @@
         <v>30</v>
       </c>
       <c r="B12" s="6">
-        <v>274</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>22</v>
+        <v>188</v>
+      </c>
+      <c r="C12" s="6">
+        <v>4</v>
+      </c>
+      <c r="D12" s="6">
+        <v>45</v>
       </c>
       <c r="E12" s="6">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G12" s="6">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="6">
-        <v>15</v>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1030,13 +1030,13 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>274</v>
+        <v>188</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>22</v>
@@ -1050,28 +1050,28 @@
         <v>30</v>
       </c>
       <c r="B13" s="6">
-        <v>188</v>
-      </c>
-      <c r="C13" s="6">
-        <v>4</v>
-      </c>
-      <c r="D13" s="6">
-        <v>45</v>
+        <v>274</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="6">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
+      <c r="I13" s="6">
+        <v>24</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1086,13 +1086,13 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>188</v>
+        <v>274</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>22</v>
@@ -1171,7 +1171,7 @@
         <v>10</v>
       </c>
       <c r="E15" s="6">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>22</v>
@@ -1198,16 +1198,16 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>560</v>
+        <v>595</v>
       </c>
       <c r="Q15" s="6">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>32</v>
@@ -1218,28 +1218,28 @@
         <v>33</v>
       </c>
       <c r="B16" s="6">
-        <v>2774</v>
+        <v>1326</v>
       </c>
       <c r="C16" s="6">
-        <v>562</v>
+        <v>112</v>
       </c>
       <c r="D16" s="6">
-        <v>1155</v>
+        <v>401</v>
       </c>
       <c r="E16" s="6">
-        <v>352</v>
+        <v>153</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="6">
-        <v>184</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>22</v>
+        <v>308</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1</v>
       </c>
       <c r="I16" s="6">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>22</v>
@@ -1254,13 +1254,13 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>430</v>
+        <v>236</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>2774</v>
+        <v>1326</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>22</v>
@@ -1274,28 +1274,28 @@
         <v>33</v>
       </c>
       <c r="B17" s="6">
-        <v>1326</v>
+        <v>2691</v>
       </c>
       <c r="C17" s="6">
-        <v>111</v>
+        <v>643</v>
       </c>
       <c r="D17" s="6">
-        <v>396</v>
+        <v>994</v>
       </c>
       <c r="E17" s="6">
-        <v>153</v>
+        <v>603</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="6">
-        <v>308</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="I17" s="6">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>22</v>
@@ -1310,13 +1310,13 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>241</v>
+        <v>385</v>
       </c>
       <c r="O17" s="6">
         <v>1</v>
       </c>
       <c r="P17" s="6">
-        <v>1326</v>
+        <v>2691</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>22</v>
@@ -1330,28 +1330,28 @@
         <v>33</v>
       </c>
       <c r="B18" s="6">
-        <v>2691</v>
+        <v>2774</v>
       </c>
       <c r="C18" s="6">
-        <v>643</v>
+        <v>562</v>
       </c>
       <c r="D18" s="6">
-        <v>994</v>
+        <v>1156</v>
       </c>
       <c r="E18" s="6">
-        <v>597</v>
+        <v>352</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>34</v>
+        <v>184</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="6">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>22</v>
@@ -1366,13 +1366,13 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>391</v>
-      </c>
-      <c r="O18" s="6">
-        <v>1</v>
+        <v>429</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>2691</v>
+        <v>2774</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>22</v>
@@ -1386,28 +1386,28 @@
         <v>34</v>
       </c>
       <c r="B19" s="6">
-        <v>390</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>22</v>
+        <v>1900</v>
+      </c>
+      <c r="C19" s="6">
+        <v>736</v>
       </c>
       <c r="D19" s="6">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E19" s="6">
-        <v>38</v>
+        <v>309</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="6">
-        <v>43</v>
+      <c r="G19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1422,13 +1422,13 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>390</v>
+        <v>1900</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>22</v>
@@ -1442,28 +1442,28 @@
         <v>34</v>
       </c>
       <c r="B20" s="6">
-        <v>1900</v>
-      </c>
-      <c r="C20" s="6">
-        <v>736</v>
+        <v>390</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D20" s="6">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="E20" s="6">
-        <v>305</v>
+        <v>78</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>22</v>
+      <c r="G20" s="6">
+        <v>43</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="6">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>22</v>
@@ -1478,13 +1478,13 @@
         <v>22</v>
       </c>
       <c r="N20" s="6">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>1900</v>
+        <v>390</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>22</v>
@@ -1498,7 +1498,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="6">
-        <v>216</v>
+        <v>336</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>22</v>
@@ -1506,20 +1506,20 @@
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>22</v>
+      <c r="E21" s="6">
+        <v>12</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="6">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>22</v>
@@ -1534,16 +1534,16 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="Q21" s="6">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>36</v>
@@ -1554,7 +1554,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="6">
-        <v>336</v>
+        <v>216</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>22</v>
@@ -1562,20 +1562,20 @@
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="6">
-        <v>12</v>
+      <c r="E22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="6">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="6">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>22</v>
@@ -1590,16 +1590,16 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="Q22" s="6">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>37</v>
@@ -1625,13 +1625,13 @@
         <v>22</v>
       </c>
       <c r="G23" s="6">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>22</v>
@@ -1646,7 +1646,7 @@
         <v>22</v>
       </c>
       <c r="N23" s="6">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>22</v>
@@ -1666,7 +1666,7 @@
         <v>39</v>
       </c>
       <c r="B24" s="6">
-        <v>324</v>
+        <v>264</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>22</v>
@@ -1675,19 +1675,19 @@
         <v>22</v>
       </c>
       <c r="E24" s="6">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="6">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="6">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>22</v>
@@ -1702,19 +1702,19 @@
         <v>22</v>
       </c>
       <c r="N24" s="6">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P24" s="6">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="Q24" s="6">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -1722,7 +1722,7 @@
         <v>39</v>
       </c>
       <c r="B25" s="6">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>22</v>
@@ -1731,13 +1731,13 @@
         <v>22</v>
       </c>
       <c r="E25" s="6">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="6">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>22</v>
@@ -1758,19 +1758,19 @@
         <v>22</v>
       </c>
       <c r="N25" s="6">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P25" s="6">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="Q25" s="6">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -1778,7 +1778,7 @@
         <v>39</v>
       </c>
       <c r="B26" s="6">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>22</v>
@@ -1787,19 +1787,19 @@
         <v>22</v>
       </c>
       <c r="E26" s="6">
+        <v>36</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="6">
         <v>60</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="6">
-        <v>92</v>
-      </c>
       <c r="H26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I26" s="6">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>22</v>
@@ -1814,19 +1814,19 @@
         <v>22</v>
       </c>
       <c r="N26" s="6">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="Q26" s="6">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -1837,13 +1837,13 @@
         <v>5441</v>
       </c>
       <c r="C27" s="6">
-        <v>2219</v>
+        <v>2645</v>
       </c>
       <c r="D27" s="6">
-        <v>217</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>22</v>
+        <v>237</v>
+      </c>
+      <c r="E27" s="6">
+        <v>10</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>22</v>
@@ -1873,13 +1873,13 @@
         <v>50</v>
       </c>
       <c r="O27" s="6">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="P27" s="6">
-        <v>2496</v>
+        <v>2983</v>
       </c>
       <c r="Q27" s="6">
-        <v>2945</v>
+        <v>2458</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>43</v>

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="46">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>69.84%</t>
+    <t>76.11%</t>
   </si>
   <si>
     <t>Extra Suite</t>
@@ -121,12 +121,12 @@
     <t>Suites Primer Nivel</t>
   </si>
   <si>
+    <t>66.67%</t>
+  </si>
+  <si>
     <t>53.87%</t>
   </si>
   <si>
-    <t>66.67%</t>
-  </si>
-  <si>
     <t>65.38%</t>
   </si>
   <si>
@@ -142,13 +142,13 @@
     <t>Tercer Nivel</t>
   </si>
   <si>
-    <t>54.82%</t>
+    <t>60.34%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>79.47%</t>
+    <t>81.97%</t>
   </si>
 </sst>
 </file>
@@ -661,10 +661,10 @@
         <v>4198</v>
       </c>
       <c r="C6" s="6">
-        <v>1795</v>
+        <v>1986</v>
       </c>
       <c r="D6" s="6">
-        <v>1035</v>
+        <v>1139</v>
       </c>
       <c r="E6" s="6">
         <v>11</v>
@@ -697,13 +697,13 @@
         <v>50</v>
       </c>
       <c r="O6" s="6">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="P6" s="6">
-        <v>2932</v>
+        <v>3195</v>
       </c>
       <c r="Q6" s="6">
-        <v>1266</v>
+        <v>1003</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -826,28 +826,28 @@
         <v>28</v>
       </c>
       <c r="B9" s="6">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="C9" s="6">
-        <v>49</v>
-      </c>
-      <c r="D9" s="6">
-        <v>29</v>
-      </c>
-      <c r="E9" s="6">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="6">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -862,13 +862,13 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>22</v>
@@ -882,28 +882,28 @@
         <v>28</v>
       </c>
       <c r="B10" s="6">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="C10" s="6">
-        <v>2</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="D10" s="6">
+        <v>29</v>
+      </c>
+      <c r="E10" s="6">
+        <v>30</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -918,13 +918,13 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>22</v>
@@ -994,13 +994,13 @@
         <v>30</v>
       </c>
       <c r="B12" s="6">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="C12" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D12" s="6">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E12" s="6">
         <v>36</v>
@@ -1008,8 +1008,8 @@
       <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="6">
-        <v>11</v>
+      <c r="G12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>22</v>
@@ -1030,13 +1030,13 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>22</v>
@@ -1050,28 +1050,28 @@
         <v>30</v>
       </c>
       <c r="B13" s="6">
-        <v>274</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>22</v>
+        <v>188</v>
+      </c>
+      <c r="C13" s="6">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6">
+        <v>45</v>
       </c>
       <c r="E13" s="6">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="6">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6">
-        <v>24</v>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1086,13 +1086,13 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>274</v>
+        <v>188</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>22</v>
@@ -1106,28 +1106,28 @@
         <v>30</v>
       </c>
       <c r="B14" s="6">
-        <v>199</v>
-      </c>
-      <c r="C14" s="6">
-        <v>10</v>
-      </c>
-      <c r="D14" s="6">
-        <v>62</v>
+        <v>274</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E14" s="6">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>22</v>
+      <c r="G14" s="6">
+        <v>100</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
+      <c r="I14" s="6">
+        <v>24</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>22</v>
@@ -1142,13 +1142,13 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>22</v>
@@ -1280,7 +1280,7 @@
         <v>643</v>
       </c>
       <c r="D17" s="6">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E17" s="6">
         <v>603</v>
@@ -1312,8 +1312,8 @@
       <c r="N17" s="6">
         <v>385</v>
       </c>
-      <c r="O17" s="6">
-        <v>1</v>
+      <c r="O17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P17" s="6">
         <v>2691</v>
@@ -1386,28 +1386,28 @@
         <v>34</v>
       </c>
       <c r="B19" s="6">
-        <v>1900</v>
-      </c>
-      <c r="C19" s="6">
-        <v>736</v>
+        <v>390</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D19" s="6">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="E19" s="6">
-        <v>309</v>
+        <v>78</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>22</v>
+      <c r="G19" s="6">
+        <v>43</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="6">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1422,13 +1422,13 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>76</v>
+        <v>225</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>1900</v>
+        <v>390</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>22</v>
@@ -1442,28 +1442,28 @@
         <v>34</v>
       </c>
       <c r="B20" s="6">
-        <v>390</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>22</v>
+        <v>1900</v>
+      </c>
+      <c r="C20" s="6">
+        <v>736</v>
       </c>
       <c r="D20" s="6">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E20" s="6">
-        <v>78</v>
+        <v>309</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="6">
-        <v>43</v>
+      <c r="G20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>22</v>
@@ -1478,13 +1478,13 @@
         <v>22</v>
       </c>
       <c r="N20" s="6">
-        <v>225</v>
+        <v>76</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>390</v>
+        <v>1900</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>22</v>
@@ -1498,7 +1498,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="6">
-        <v>336</v>
+        <v>216</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>22</v>
@@ -1506,20 +1506,20 @@
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="6">
-        <v>12</v>
+      <c r="E21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="6">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>22</v>
@@ -1534,16 +1534,16 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="Q21" s="6">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>36</v>
@@ -1554,7 +1554,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="6">
-        <v>216</v>
+        <v>336</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>22</v>
@@ -1562,20 +1562,20 @@
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>22</v>
+      <c r="E22" s="6">
+        <v>12</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="6">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="6">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>22</v>
@@ -1590,16 +1590,16 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="Q22" s="6">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>37</v>
@@ -1714,7 +1714,7 @@
         <v>88</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -1837,10 +1837,10 @@
         <v>5441</v>
       </c>
       <c r="C27" s="6">
-        <v>2645</v>
+        <v>2894</v>
       </c>
       <c r="D27" s="6">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="E27" s="6">
         <v>10</v>
@@ -1873,13 +1873,13 @@
         <v>50</v>
       </c>
       <c r="O27" s="6">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="P27" s="6">
-        <v>2983</v>
+        <v>3283</v>
       </c>
       <c r="Q27" s="6">
-        <v>2458</v>
+        <v>2158</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>43</v>

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="45">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>76.11%</t>
+    <t>79.61%</t>
   </si>
   <si>
     <t>Extra Suite</t>
@@ -109,9 +109,6 @@
     <t>Parrilladas</t>
   </si>
   <si>
-    <t>94.44%</t>
-  </si>
-  <si>
     <t>Primer Nivel</t>
   </si>
   <si>
@@ -124,7 +121,7 @@
     <t>66.67%</t>
   </si>
   <si>
-    <t>53.87%</t>
+    <t>57.44%</t>
   </si>
   <si>
     <t>65.38%</t>
@@ -133,22 +130,22 @@
     <t>Suites Segundo Nivel</t>
   </si>
   <si>
+    <t>58.02%</t>
+  </si>
+  <si>
     <t>59.57%</t>
   </si>
   <si>
-    <t>58.02%</t>
-  </si>
-  <si>
     <t>Tercer Nivel</t>
   </si>
   <si>
-    <t>60.34%</t>
+    <t>65.94%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>81.97%</t>
+    <t>84.18%</t>
   </si>
 </sst>
 </file>
@@ -661,10 +658,10 @@
         <v>4198</v>
       </c>
       <c r="C6" s="6">
-        <v>1986</v>
+        <v>2073</v>
       </c>
       <c r="D6" s="6">
-        <v>1139</v>
+        <v>1190</v>
       </c>
       <c r="E6" s="6">
         <v>11</v>
@@ -697,13 +694,13 @@
         <v>50</v>
       </c>
       <c r="O6" s="6">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="P6" s="6">
-        <v>3195</v>
+        <v>3342</v>
       </c>
       <c r="Q6" s="6">
-        <v>1003</v>
+        <v>856</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -891,7 +888,7 @@
         <v>29</v>
       </c>
       <c r="E10" s="6">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -918,7 +915,7 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
@@ -1003,7 +1000,7 @@
         <v>62</v>
       </c>
       <c r="E12" s="6">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1030,7 +1027,7 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
@@ -1050,28 +1047,28 @@
         <v>30</v>
       </c>
       <c r="B13" s="6">
-        <v>188</v>
-      </c>
-      <c r="C13" s="6">
-        <v>4</v>
-      </c>
-      <c r="D13" s="6">
-        <v>45</v>
+        <v>274</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="6">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
+      <c r="I13" s="6">
+        <v>24</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1086,13 +1083,13 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>188</v>
+        <v>274</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>22</v>
@@ -1106,28 +1103,28 @@
         <v>30</v>
       </c>
       <c r="B14" s="6">
-        <v>274</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
+        <v>188</v>
+      </c>
+      <c r="C14" s="6">
+        <v>4</v>
+      </c>
+      <c r="D14" s="6">
+        <v>45</v>
       </c>
       <c r="E14" s="6">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="6">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="6">
-        <v>24</v>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>22</v>
@@ -1142,13 +1139,13 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>274</v>
+        <v>188</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>22</v>
@@ -1165,7 +1162,7 @@
         <v>630</v>
       </c>
       <c r="C15" s="6">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="D15" s="6">
         <v>10</v>
@@ -1198,48 +1195,48 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>595</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>35</v>
+        <v>630</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="6">
-        <v>1326</v>
+        <v>2774</v>
       </c>
       <c r="C16" s="6">
-        <v>112</v>
+        <v>568</v>
       </c>
       <c r="D16" s="6">
-        <v>401</v>
+        <v>1156</v>
       </c>
       <c r="E16" s="6">
-        <v>153</v>
+        <v>388</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="6">
-        <v>308</v>
-      </c>
-      <c r="H16" s="6">
-        <v>1</v>
+        <v>184</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="I16" s="6">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>22</v>
@@ -1254,13 +1251,13 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>236</v>
+        <v>387</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>1326</v>
+        <v>2774</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>22</v>
@@ -1271,7 +1268,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="6">
         <v>2691</v>
@@ -1283,7 +1280,7 @@
         <v>995</v>
       </c>
       <c r="E17" s="6">
-        <v>603</v>
+        <v>663</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
@@ -1310,7 +1307,7 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>385</v>
+        <v>325</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
@@ -1327,31 +1324,31 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="6">
-        <v>2774</v>
+        <v>1326</v>
       </c>
       <c r="C18" s="6">
-        <v>562</v>
+        <v>112</v>
       </c>
       <c r="D18" s="6">
-        <v>1156</v>
+        <v>401</v>
       </c>
       <c r="E18" s="6">
-        <v>352</v>
+        <v>184</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>184</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>22</v>
+        <v>308</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1</v>
       </c>
       <c r="I18" s="6">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>22</v>
@@ -1366,13 +1363,13 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>429</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>22</v>
+        <v>201</v>
+      </c>
+      <c r="O18" s="6">
+        <v>4</v>
       </c>
       <c r="P18" s="6">
-        <v>2774</v>
+        <v>1326</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>22</v>
@@ -1383,31 +1380,31 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="6">
-        <v>390</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>22</v>
+        <v>1900</v>
+      </c>
+      <c r="C19" s="6">
+        <v>736</v>
       </c>
       <c r="D19" s="6">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E19" s="6">
-        <v>78</v>
+        <v>309</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="6">
-        <v>43</v>
+      <c r="G19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1422,13 +1419,13 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>225</v>
+        <v>76</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>390</v>
+        <v>1900</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>22</v>
@@ -1439,31 +1436,31 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="6">
-        <v>1900</v>
-      </c>
-      <c r="C20" s="6">
-        <v>736</v>
+        <v>390</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D20" s="6">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="E20" s="6">
-        <v>309</v>
+        <v>80</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>22</v>
+      <c r="G20" s="6">
+        <v>43</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="6">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>22</v>
@@ -1478,13 +1475,13 @@
         <v>22</v>
       </c>
       <c r="N20" s="6">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>1900</v>
+        <v>390</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>22</v>
@@ -1495,7 +1492,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="6">
         <v>216</v>
@@ -1546,18 +1543,18 @@
         <v>72</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="6">
         <v>336</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>22</v>
+      <c r="C22" s="6">
+        <v>12</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>22</v>
@@ -1596,18 +1593,18 @@
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="Q22" s="6">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="6">
         <v>312</v>
@@ -1658,12 +1655,12 @@
         <v>108</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="6">
         <v>264</v>
@@ -1714,71 +1711,71 @@
         <v>88</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="6">
+        <v>262</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="6">
+        <v>36</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="6">
+        <v>60</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="6">
+        <v>20</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" s="6">
+        <v>36</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P25" s="6">
+        <v>152</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>110</v>
+      </c>
+      <c r="R25" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="B25" s="6">
-        <v>324</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="6">
-        <v>25</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="6">
-        <v>112</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="6">
-        <v>8</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N25" s="6">
-        <v>48</v>
-      </c>
-      <c r="O25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P25" s="6">
-        <v>193</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>131</v>
-      </c>
-      <c r="R25" s="6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="6">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>22</v>
@@ -1787,19 +1784,19 @@
         <v>22</v>
       </c>
       <c r="E26" s="6">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="6">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I26" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>22</v>
@@ -1814,36 +1811,36 @@
         <v>22</v>
       </c>
       <c r="N26" s="6">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="Q26" s="6">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="6">
         <v>5441</v>
       </c>
       <c r="C27" s="6">
-        <v>2894</v>
+        <v>2998</v>
       </c>
       <c r="D27" s="6">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="E27" s="6">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>22</v>
@@ -1873,21 +1870,21 @@
         <v>50</v>
       </c>
       <c r="O27" s="6">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="P27" s="6">
-        <v>3283</v>
+        <v>3588</v>
       </c>
       <c r="Q27" s="6">
-        <v>2158</v>
+        <v>1853</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" s="7">
         <f>SUM(B6:B27)</f>
@@ -1938,7 +1935,7 @@
         <f>SUM(Q6:Q27)</f>
       </c>
       <c r="R28" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="44">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>79.61%</t>
+    <t>93.31%</t>
   </si>
   <si>
     <t>Extra Suite</t>
   </si>
   <si>
-    <t>0.00%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>PCD</t>
@@ -100,9 +100,6 @@
     <t>Palco Azul</t>
   </si>
   <si>
-    <t>100.00%</t>
-  </si>
-  <si>
     <t>Palco Rojo</t>
   </si>
   <si>
@@ -121,12 +118,12 @@
     <t>66.67%</t>
   </si>
   <si>
+    <t>65.38%</t>
+  </si>
+  <si>
     <t>57.44%</t>
   </si>
   <si>
-    <t>65.38%</t>
-  </si>
-  <si>
     <t>Suites Segundo Nivel</t>
   </si>
   <si>
@@ -139,13 +136,13 @@
     <t>Tercer Nivel</t>
   </si>
   <si>
-    <t>65.94%</t>
+    <t>80.68%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>84.18%</t>
+    <t>91.16%</t>
   </si>
 </sst>
 </file>
@@ -658,10 +655,10 @@
         <v>4198</v>
       </c>
       <c r="C6" s="6">
-        <v>2073</v>
+        <v>2445</v>
       </c>
       <c r="D6" s="6">
-        <v>1190</v>
+        <v>1382</v>
       </c>
       <c r="E6" s="6">
         <v>11</v>
@@ -691,16 +688,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="O6" s="6">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="P6" s="6">
-        <v>3342</v>
+        <v>3917</v>
       </c>
       <c r="Q6" s="6">
-        <v>856</v>
+        <v>281</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -746,17 +743,17 @@
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>22</v>
+      <c r="N7" s="6">
+        <v>200</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q7" s="6">
+      <c r="P7" s="6">
         <v>200</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -871,7 +868,7 @@
         <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -882,7 +879,7 @@
         <v>189</v>
       </c>
       <c r="C10" s="6">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" s="6">
         <v>29</v>
@@ -915,10 +912,10 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>54</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
+        <v>46</v>
+      </c>
+      <c r="O10" s="6">
+        <v>6</v>
       </c>
       <c r="P10" s="6">
         <v>189</v>
@@ -927,7 +924,7 @@
         <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -983,12 +980,12 @@
         <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="6">
         <v>199</v>
@@ -1039,12 +1036,12 @@
         <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="6">
         <v>274</v>
@@ -1068,7 +1065,7 @@
         <v>22</v>
       </c>
       <c r="I13" s="6">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1083,7 +1080,7 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
@@ -1095,18 +1092,18 @@
         <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="6">
         <v>188</v>
       </c>
       <c r="C14" s="6">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D14" s="6">
         <v>45</v>
@@ -1139,7 +1136,7 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
@@ -1151,12 +1148,12 @@
         <v>22</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="6">
         <v>630</v>
@@ -1207,24 +1204,24 @@
         <v>22</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="6">
         <v>2774</v>
       </c>
       <c r="C16" s="6">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="D16" s="6">
         <v>1156</v>
       </c>
       <c r="E16" s="6">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
@@ -1251,7 +1248,7 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>387</v>
+        <v>360</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
@@ -1263,36 +1260,36 @@
         <v>22</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="6">
-        <v>2691</v>
+        <v>1326</v>
       </c>
       <c r="C17" s="6">
-        <v>643</v>
+        <v>114</v>
       </c>
       <c r="D17" s="6">
-        <v>995</v>
+        <v>401</v>
       </c>
       <c r="E17" s="6">
-        <v>663</v>
+        <v>188</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="6">
-        <v>34</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>22</v>
+        <v>308</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
       </c>
       <c r="I17" s="6">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>22</v>
@@ -1307,48 +1304,48 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>325</v>
+        <v>199</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>2691</v>
+        <v>1326</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" s="6">
-        <v>1326</v>
+        <v>2691</v>
       </c>
       <c r="C18" s="6">
-        <v>112</v>
+        <v>645</v>
       </c>
       <c r="D18" s="6">
-        <v>401</v>
+        <v>995</v>
       </c>
       <c r="E18" s="6">
-        <v>184</v>
+        <v>668</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>308</v>
-      </c>
-      <c r="H18" s="6">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="I18" s="6">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>22</v>
@@ -1363,24 +1360,24 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>201</v>
-      </c>
-      <c r="O18" s="6">
-        <v>4</v>
+        <v>312</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>1326</v>
+        <v>2691</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="6">
         <v>1900</v>
@@ -1392,7 +1389,7 @@
         <v>778</v>
       </c>
       <c r="E19" s="6">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
@@ -1419,7 +1416,7 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
@@ -1431,12 +1428,12 @@
         <v>22</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="6">
         <v>390</v>
@@ -1487,12 +1484,12 @@
         <v>22</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="6">
         <v>216</v>
@@ -1543,18 +1540,18 @@
         <v>72</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="6">
-        <v>336</v>
-      </c>
-      <c r="C22" s="6">
-        <v>12</v>
+        <v>312</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>22</v>
@@ -1566,13 +1563,13 @@
         <v>22</v>
       </c>
       <c r="G22" s="6">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>22</v>
@@ -1587,30 +1584,30 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="Q22" s="6">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="6">
-        <v>312</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>22</v>
+        <v>336</v>
+      </c>
+      <c r="C23" s="6">
+        <v>12</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>22</v>
@@ -1622,13 +1619,13 @@
         <v>22</v>
       </c>
       <c r="G23" s="6">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="6">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>22</v>
@@ -1643,83 +1640,83 @@
         <v>22</v>
       </c>
       <c r="N23" s="6">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="Q23" s="6">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="6">
+        <v>262</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="6">
+        <v>36</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="6">
+        <v>60</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="6">
+        <v>20</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="6">
+        <v>36</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" s="6">
+        <v>152</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>110</v>
+      </c>
+      <c r="R24" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="B24" s="6">
-        <v>264</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="6">
-        <v>48</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="6">
-        <v>92</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="6">
-        <v>24</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N24" s="6">
-        <v>12</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P24" s="6">
-        <v>176</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>88</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="6">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>22</v>
@@ -1728,19 +1725,19 @@
         <v>22</v>
       </c>
       <c r="E25" s="6">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="6">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I25" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>22</v>
@@ -1755,16 +1752,16 @@
         <v>22</v>
       </c>
       <c r="N25" s="6">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P25" s="6">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="Q25" s="6">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>39</v>
@@ -1772,10 +1769,10 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6">
-        <v>324</v>
+        <v>264</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>22</v>
@@ -1784,19 +1781,19 @@
         <v>22</v>
       </c>
       <c r="E26" s="6">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="6">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I26" s="6">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>22</v>
@@ -1811,36 +1808,36 @@
         <v>22</v>
       </c>
       <c r="N26" s="6">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="Q26" s="6">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="6">
         <v>5441</v>
       </c>
       <c r="C27" s="6">
-        <v>2998</v>
+        <v>3574</v>
       </c>
       <c r="D27" s="6">
-        <v>361</v>
+        <v>528</v>
       </c>
       <c r="E27" s="6">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>22</v>
@@ -1867,24 +1864,24 @@
         <v>22</v>
       </c>
       <c r="N27" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O27" s="6">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="P27" s="6">
-        <v>3588</v>
+        <v>4390</v>
       </c>
       <c r="Q27" s="6">
-        <v>1853</v>
+        <v>1051</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="7">
         <f>SUM(B6:B27)</f>
@@ -1935,7 +1932,7 @@
         <f>SUM(Q6:Q27)</f>
       </c>
       <c r="R28" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="43">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,15 +82,12 @@
     <t>-</t>
   </si>
   <si>
-    <t>93.31%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Extra Suite</t>
   </si>
   <si>
-    <t>100.00%</t>
-  </si>
-  <si>
     <t>PCD</t>
   </si>
   <si>
@@ -115,12 +112,12 @@
     <t>Suites Primer Nivel</t>
   </si>
   <si>
+    <t>65.38%</t>
+  </si>
+  <si>
     <t>66.67%</t>
   </si>
   <si>
-    <t>65.38%</t>
-  </si>
-  <si>
     <t>57.44%</t>
   </si>
   <si>
@@ -136,13 +133,13 @@
     <t>Tercer Nivel</t>
   </si>
   <si>
-    <t>80.68%</t>
+    <t>90.90%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>91.16%</t>
+    <t>94.87%</t>
   </si>
 </sst>
 </file>
@@ -655,13 +652,13 @@
         <v>4198</v>
       </c>
       <c r="C6" s="6">
-        <v>2445</v>
+        <v>2554</v>
       </c>
       <c r="D6" s="6">
-        <v>1382</v>
+        <v>1445</v>
       </c>
       <c r="E6" s="6">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -688,16 +685,16 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="O6" s="6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P6" s="6">
-        <v>3917</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>281</v>
+        <v>4198</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -756,12 +753,12 @@
         <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="6">
         <v>14</v>
@@ -812,36 +809,36 @@
         <v>12</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="6">
-        <v>265</v>
+        <v>186</v>
       </c>
       <c r="C9" s="6">
-        <v>2</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="D9" s="6">
+        <v>35</v>
+      </c>
+      <c r="E9" s="6">
+        <v>36</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="6">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="6">
-        <v>24</v>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -856,48 +853,48 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>265</v>
+        <v>186</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="6">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="C10" s="6">
-        <v>51</v>
-      </c>
-      <c r="D10" s="6">
-        <v>29</v>
-      </c>
-      <c r="E10" s="6">
-        <v>34</v>
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -912,48 +909,48 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>46</v>
-      </c>
-      <c r="O10" s="6">
-        <v>6</v>
+        <v>81</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="6">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C11" s="6">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="D11" s="6">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E11" s="6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>22</v>
+      <c r="I11" s="6">
+        <v>15</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -968,42 +965,42 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="6">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C12" s="6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D12" s="6">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E12" s="6">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>22</v>
+      <c r="G12" s="6">
+        <v>11</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>22</v>
@@ -1024,48 +1021,48 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="6">
-        <v>274</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>22</v>
+        <v>199</v>
+      </c>
+      <c r="C13" s="6">
+        <v>10</v>
+      </c>
+      <c r="D13" s="6">
+        <v>62</v>
       </c>
       <c r="E13" s="6">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="6">
-        <v>100</v>
+      <c r="G13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6">
-        <v>33</v>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1080,48 +1077,48 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>274</v>
+        <v>199</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="6">
-        <v>188</v>
-      </c>
-      <c r="C14" s="6">
-        <v>17</v>
-      </c>
-      <c r="D14" s="6">
-        <v>45</v>
+        <v>274</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E14" s="6">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="6">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
+      <c r="I14" s="6">
+        <v>33</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>22</v>
@@ -1136,24 +1133,24 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>188</v>
+        <v>274</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="6">
         <v>630</v>
@@ -1204,36 +1201,36 @@
         <v>22</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="6">
-        <v>2774</v>
+        <v>2691</v>
       </c>
       <c r="C16" s="6">
-        <v>575</v>
+        <v>645</v>
       </c>
       <c r="D16" s="6">
-        <v>1156</v>
+        <v>995</v>
       </c>
       <c r="E16" s="6">
-        <v>408</v>
+        <v>668</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="6">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="6">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>22</v>
@@ -1248,48 +1245,48 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>2774</v>
+        <v>2691</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="6">
-        <v>1326</v>
+        <v>2774</v>
       </c>
       <c r="C17" s="6">
-        <v>114</v>
+        <v>575</v>
       </c>
       <c r="D17" s="6">
-        <v>401</v>
+        <v>1156</v>
       </c>
       <c r="E17" s="6">
-        <v>188</v>
+        <v>413</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="6">
-        <v>308</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1</v>
+        <v>184</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="I17" s="6">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>22</v>
@@ -1304,48 +1301,48 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>199</v>
+        <v>355</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>1326</v>
+        <v>2774</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6">
-        <v>2691</v>
+        <v>1326</v>
       </c>
       <c r="C18" s="6">
-        <v>645</v>
+        <v>114</v>
       </c>
       <c r="D18" s="6">
-        <v>995</v>
+        <v>401</v>
       </c>
       <c r="E18" s="6">
-        <v>668</v>
+        <v>188</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>34</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>22</v>
+        <v>308</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1</v>
       </c>
       <c r="I18" s="6">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>22</v>
@@ -1360,24 +1357,24 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>312</v>
+        <v>199</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>2691</v>
+        <v>1326</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="6">
         <v>1900</v>
@@ -1428,12 +1425,12 @@
         <v>22</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="6">
         <v>390</v>
@@ -1484,15 +1481,15 @@
         <v>22</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="6">
-        <v>216</v>
+        <v>312</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>22</v>
@@ -1500,14 +1497,14 @@
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>22</v>
+      <c r="E21" s="6">
+        <v>12</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="6">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>22</v>
@@ -1528,27 +1525,27 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="Q21" s="6">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="6">
-        <v>312</v>
+        <v>216</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>22</v>
@@ -1556,14 +1553,14 @@
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="6">
-        <v>12</v>
+      <c r="E22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="6">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>22</v>
@@ -1584,24 +1581,24 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="Q22" s="6">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="6">
         <v>336</v>
@@ -1652,12 +1649,12 @@
         <v>143</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="6">
         <v>262</v>
@@ -1708,15 +1705,15 @@
         <v>110</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="6">
-        <v>324</v>
+        <v>264</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>22</v>
@@ -1725,19 +1722,19 @@
         <v>22</v>
       </c>
       <c r="E25" s="6">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="6">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I25" s="6">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>22</v>
@@ -1752,27 +1749,27 @@
         <v>22</v>
       </c>
       <c r="N25" s="6">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P25" s="6">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="Q25" s="6">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="6">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>22</v>
@@ -1781,63 +1778,63 @@
         <v>22</v>
       </c>
       <c r="E26" s="6">
+        <v>25</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="6">
+        <v>112</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="6">
+        <v>8</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="6">
         <v>48</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="6">
-        <v>92</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="6">
-        <v>24</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" s="6">
-        <v>12</v>
-      </c>
       <c r="O26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="Q26" s="6">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="6">
         <v>5441</v>
       </c>
       <c r="C27" s="6">
-        <v>3574</v>
+        <v>3832</v>
       </c>
       <c r="D27" s="6">
-        <v>528</v>
+        <v>635</v>
       </c>
       <c r="E27" s="6">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>22</v>
@@ -1864,24 +1861,24 @@
         <v>22</v>
       </c>
       <c r="N27" s="6">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="O27" s="6">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="P27" s="6">
-        <v>4390</v>
+        <v>4946</v>
       </c>
       <c r="Q27" s="6">
-        <v>1051</v>
+        <v>495</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="7">
         <f>SUM(B6:B27)</f>
@@ -1932,7 +1929,7 @@
         <f>SUM(Q6:Q27)</f>
       </c>
       <c r="R28" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="42">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -112,34 +112,31 @@
     <t>Suites Primer Nivel</t>
   </si>
   <si>
+    <t>66.67%</t>
+  </si>
+  <si>
+    <t>57.44%</t>
+  </si>
+  <si>
     <t>65.38%</t>
   </si>
   <si>
-    <t>66.67%</t>
-  </si>
-  <si>
-    <t>57.44%</t>
-  </si>
-  <si>
     <t>Suites Segundo Nivel</t>
   </si>
   <si>
+    <t>59.57%</t>
+  </si>
+  <si>
     <t>58.02%</t>
   </si>
   <si>
-    <t>59.57%</t>
-  </si>
-  <si>
     <t>Tercer Nivel</t>
   </si>
   <si>
-    <t>90.90%</t>
-  </si>
-  <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>94.87%</t>
+    <t>97.06%</t>
   </si>
 </sst>
 </file>
@@ -652,13 +649,13 @@
         <v>4198</v>
       </c>
       <c r="C6" s="6">
-        <v>2554</v>
+        <v>2565</v>
       </c>
       <c r="D6" s="6">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="E6" s="6">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>22</v>
@@ -685,10 +682,10 @@
         <v>22</v>
       </c>
       <c r="N6" s="6">
-        <v>120</v>
-      </c>
-      <c r="O6" s="6">
-        <v>14</v>
+        <v>100</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
         <v>4198</v>
@@ -873,28 +870,28 @@
         <v>27</v>
       </c>
       <c r="B10" s="6">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="C10" s="6">
-        <v>2</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>22</v>
+        <v>57</v>
+      </c>
+      <c r="D10" s="6">
+        <v>29</v>
+      </c>
+      <c r="E10" s="6">
+        <v>34</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -909,13 +906,13 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>22</v>
@@ -929,28 +926,28 @@
         <v>27</v>
       </c>
       <c r="B11" s="6">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="C11" s="6">
-        <v>57</v>
-      </c>
-      <c r="D11" s="6">
-        <v>29</v>
-      </c>
-      <c r="E11" s="6">
-        <v>34</v>
+        <v>2</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -965,13 +962,13 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>22</v>
@@ -985,22 +982,22 @@
         <v>28</v>
       </c>
       <c r="B12" s="6">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="C12" s="6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D12" s="6">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E12" s="6">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="6">
-        <v>11</v>
+      <c r="G12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>22</v>
@@ -1021,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>22</v>
@@ -1041,28 +1038,28 @@
         <v>28</v>
       </c>
       <c r="B13" s="6">
-        <v>199</v>
-      </c>
-      <c r="C13" s="6">
+        <v>274</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="6">
         <v>10</v>
       </c>
-      <c r="D13" s="6">
-        <v>62</v>
-      </c>
-      <c r="E13" s="6">
-        <v>60</v>
-      </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
+      <c r="G13" s="6">
+        <v>100</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
+      <c r="I13" s="6">
+        <v>33</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1077,13 +1074,13 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>22</v>
@@ -1097,28 +1094,28 @@
         <v>28</v>
       </c>
       <c r="B14" s="6">
-        <v>274</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
+        <v>188</v>
+      </c>
+      <c r="C14" s="6">
+        <v>19</v>
+      </c>
+      <c r="D14" s="6">
+        <v>45</v>
       </c>
       <c r="E14" s="6">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="6">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="6">
-        <v>33</v>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>22</v>
@@ -1133,13 +1130,13 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>274</v>
+        <v>188</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>22</v>
@@ -1209,28 +1206,28 @@
         <v>30</v>
       </c>
       <c r="B16" s="6">
-        <v>2691</v>
+        <v>2774</v>
       </c>
       <c r="C16" s="6">
-        <v>645</v>
+        <v>575</v>
       </c>
       <c r="D16" s="6">
-        <v>995</v>
+        <v>1156</v>
       </c>
       <c r="E16" s="6">
-        <v>668</v>
+        <v>427</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="6">
-        <v>34</v>
+        <v>184</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="6">
-        <v>37</v>
+        <v>214</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>22</v>
@@ -1245,13 +1242,13 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>312</v>
+        <v>218</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>2691</v>
+        <v>2774</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>22</v>
@@ -1265,28 +1262,28 @@
         <v>30</v>
       </c>
       <c r="B17" s="6">
-        <v>2774</v>
+        <v>2691</v>
       </c>
       <c r="C17" s="6">
-        <v>575</v>
+        <v>662</v>
       </c>
       <c r="D17" s="6">
-        <v>1156</v>
+        <v>995</v>
       </c>
       <c r="E17" s="6">
-        <v>413</v>
+        <v>677</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="6">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="6">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>22</v>
@@ -1301,13 +1298,13 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>355</v>
+        <v>286</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>2774</v>
+        <v>2691</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>22</v>
@@ -1324,10 +1321,10 @@
         <v>1326</v>
       </c>
       <c r="C18" s="6">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D18" s="6">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E18" s="6">
         <v>188</v>
@@ -1336,7 +1333,7 @@
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H18" s="6">
         <v>1</v>
@@ -1357,7 +1354,7 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
@@ -1386,7 +1383,7 @@
         <v>778</v>
       </c>
       <c r="E19" s="6">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
@@ -1413,10 +1410,10 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>67</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>22</v>
+        <v>57</v>
+      </c>
+      <c r="O19" s="6">
+        <v>7</v>
       </c>
       <c r="P19" s="6">
         <v>1900</v>
@@ -1442,7 +1439,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="6">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
@@ -1469,7 +1466,7 @@
         <v>22</v>
       </c>
       <c r="N20" s="6">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
@@ -1489,7 +1486,7 @@
         <v>32</v>
       </c>
       <c r="B21" s="6">
-        <v>312</v>
+        <v>216</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>22</v>
@@ -1497,14 +1494,14 @@
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="6">
-        <v>12</v>
+      <c r="E21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="6">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>22</v>
@@ -1525,16 +1522,16 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="Q21" s="6">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>33</v>
@@ -1545,28 +1542,28 @@
         <v>32</v>
       </c>
       <c r="B22" s="6">
-        <v>216</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>22</v>
+        <v>336</v>
+      </c>
+      <c r="C22" s="6">
+        <v>12</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>22</v>
+      <c r="E22" s="6">
+        <v>12</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="6">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="6">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>22</v>
@@ -1581,16 +1578,16 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="Q22" s="6">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>34</v>
@@ -1601,10 +1598,10 @@
         <v>32</v>
       </c>
       <c r="B23" s="6">
-        <v>336</v>
-      </c>
-      <c r="C23" s="6">
-        <v>12</v>
+        <v>312</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>22</v>
@@ -1616,13 +1613,13 @@
         <v>22</v>
       </c>
       <c r="G23" s="6">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>22</v>
@@ -1637,16 +1634,16 @@
         <v>22</v>
       </c>
       <c r="N23" s="6">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="Q23" s="6">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>35</v>
@@ -1657,7 +1654,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="6">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>22</v>
@@ -1666,19 +1663,19 @@
         <v>22</v>
       </c>
       <c r="E24" s="6">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="6">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>22</v>
@@ -1693,16 +1690,16 @@
         <v>22</v>
       </c>
       <c r="N24" s="6">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P24" s="6">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="Q24" s="6">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>37</v>
@@ -1761,7 +1758,7 @@
         <v>88</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -1769,7 +1766,7 @@
         <v>36</v>
       </c>
       <c r="B26" s="6">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>22</v>
@@ -1778,19 +1775,19 @@
         <v>22</v>
       </c>
       <c r="E26" s="6">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="6">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I26" s="6">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>22</v>
@@ -1805,16 +1802,16 @@
         <v>22</v>
       </c>
       <c r="N26" s="6">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="Q26" s="6">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>38</v>
@@ -1828,13 +1825,13 @@
         <v>5441</v>
       </c>
       <c r="C27" s="6">
-        <v>3832</v>
+        <v>4248</v>
       </c>
       <c r="D27" s="6">
-        <v>635</v>
+        <v>757</v>
       </c>
       <c r="E27" s="6">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>22</v>
@@ -1861,24 +1858,24 @@
         <v>22</v>
       </c>
       <c r="N27" s="6">
-        <v>250</v>
-      </c>
-      <c r="O27" s="6">
-        <v>43</v>
+        <v>196</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P27" s="6">
-        <v>4946</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>495</v>
+        <v>5441</v>
+      </c>
+      <c r="Q27" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="7">
         <f>SUM(B6:B27)</f>
@@ -1929,7 +1926,7 @@
         <f>SUM(Q6:Q27)</f>
       </c>
       <c r="R28" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -112,31 +112,31 @@
     <t>Suites Primer Nivel</t>
   </si>
   <si>
+    <t>62.20%</t>
+  </si>
+  <si>
     <t>66.67%</t>
   </si>
   <si>
-    <t>57.44%</t>
-  </si>
-  <si>
     <t>65.38%</t>
   </si>
   <si>
     <t>Suites Segundo Nivel</t>
   </si>
   <si>
+    <t>58.02%</t>
+  </si>
+  <si>
     <t>59.57%</t>
   </si>
   <si>
-    <t>58.02%</t>
-  </si>
-  <si>
     <t>Tercer Nivel</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>97.06%</t>
+    <t>97.13%</t>
   </si>
 </sst>
 </file>
@@ -870,28 +870,28 @@
         <v>27</v>
       </c>
       <c r="B10" s="6">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="C10" s="6">
-        <v>57</v>
-      </c>
-      <c r="D10" s="6">
-        <v>29</v>
-      </c>
-      <c r="E10" s="6">
-        <v>34</v>
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -906,13 +906,13 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>22</v>
@@ -926,28 +926,28 @@
         <v>27</v>
       </c>
       <c r="B11" s="6">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="C11" s="6">
-        <v>2</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
+        <v>57</v>
+      </c>
+      <c r="D11" s="6">
+        <v>29</v>
+      </c>
+      <c r="E11" s="6">
+        <v>34</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -962,13 +962,13 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>22</v>
@@ -1262,28 +1262,28 @@
         <v>30</v>
       </c>
       <c r="B17" s="6">
-        <v>2691</v>
+        <v>1326</v>
       </c>
       <c r="C17" s="6">
-        <v>662</v>
+        <v>116</v>
       </c>
       <c r="D17" s="6">
-        <v>995</v>
+        <v>406</v>
       </c>
       <c r="E17" s="6">
-        <v>677</v>
+        <v>188</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="6">
-        <v>34</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>22</v>
+        <v>309</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
       </c>
       <c r="I17" s="6">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>22</v>
@@ -1298,13 +1298,13 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>286</v>
+        <v>191</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>2691</v>
+        <v>1326</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>22</v>
@@ -1318,28 +1318,28 @@
         <v>30</v>
       </c>
       <c r="B18" s="6">
-        <v>1326</v>
+        <v>2691</v>
       </c>
       <c r="C18" s="6">
-        <v>116</v>
+        <v>662</v>
       </c>
       <c r="D18" s="6">
-        <v>406</v>
+        <v>995</v>
       </c>
       <c r="E18" s="6">
-        <v>188</v>
+        <v>679</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>309</v>
-      </c>
-      <c r="H18" s="6">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="I18" s="6">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>22</v>
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>191</v>
+        <v>284</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>1326</v>
+        <v>2691</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>22</v>
@@ -1374,28 +1374,28 @@
         <v>31</v>
       </c>
       <c r="B19" s="6">
-        <v>1900</v>
-      </c>
-      <c r="C19" s="6">
-        <v>736</v>
+        <v>390</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D19" s="6">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="E19" s="6">
-        <v>321</v>
+        <v>124</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>22</v>
+      <c r="G19" s="6">
+        <v>43</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="6">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1410,13 +1410,13 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>57</v>
-      </c>
-      <c r="O19" s="6">
-        <v>7</v>
+        <v>179</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>1900</v>
+        <v>390</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>22</v>
@@ -1430,28 +1430,28 @@
         <v>31</v>
       </c>
       <c r="B20" s="6">
-        <v>390</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>22</v>
+        <v>1900</v>
+      </c>
+      <c r="C20" s="6">
+        <v>736</v>
       </c>
       <c r="D20" s="6">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E20" s="6">
-        <v>110</v>
+        <v>321</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="6">
-        <v>43</v>
+      <c r="G20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>22</v>
@@ -1466,13 +1466,13 @@
         <v>22</v>
       </c>
       <c r="N20" s="6">
-        <v>193</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>22</v>
+        <v>57</v>
+      </c>
+      <c r="O20" s="6">
+        <v>7</v>
       </c>
       <c r="P20" s="6">
-        <v>390</v>
+        <v>1900</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>22</v>
@@ -1486,28 +1486,28 @@
         <v>32</v>
       </c>
       <c r="B21" s="6">
-        <v>216</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>22</v>
+        <v>336</v>
+      </c>
+      <c r="C21" s="6">
+        <v>12</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>22</v>
+      <c r="E21" s="6">
+        <v>28</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="6">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>22</v>
@@ -1522,16 +1522,16 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>144</v>
+        <v>209</v>
       </c>
       <c r="Q21" s="6">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>33</v>
@@ -1542,28 +1542,28 @@
         <v>32</v>
       </c>
       <c r="B22" s="6">
-        <v>336</v>
-      </c>
-      <c r="C22" s="6">
-        <v>12</v>
+        <v>216</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="6">
-        <v>12</v>
+      <c r="E22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="6">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>22</v>
@@ -1578,16 +1578,16 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="Q22" s="6">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>34</v>
@@ -1654,7 +1654,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="6">
-        <v>324</v>
+        <v>264</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>22</v>
@@ -1663,19 +1663,19 @@
         <v>22</v>
       </c>
       <c r="E24" s="6">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="6">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="6">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>22</v>
@@ -1690,19 +1690,19 @@
         <v>22</v>
       </c>
       <c r="N24" s="6">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P24" s="6">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="Q24" s="6">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -1710,7 +1710,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="6">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>22</v>
@@ -1719,19 +1719,19 @@
         <v>22</v>
       </c>
       <c r="E25" s="6">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="6">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I25" s="6">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>22</v>
@@ -1746,19 +1746,19 @@
         <v>22</v>
       </c>
       <c r="N25" s="6">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P25" s="6">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="Q25" s="6">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -1766,7 +1766,7 @@
         <v>36</v>
       </c>
       <c r="B26" s="6">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>22</v>
@@ -1775,19 +1775,19 @@
         <v>22</v>
       </c>
       <c r="E26" s="6">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I26" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>22</v>
@@ -1802,16 +1802,16 @@
         <v>22</v>
       </c>
       <c r="N26" s="6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="Q26" s="6">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>38</v>

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="42">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -112,22 +112,22 @@
     <t>Suites Primer Nivel</t>
   </si>
   <si>
-    <t>62.20%</t>
-  </si>
-  <si>
     <t>66.67%</t>
   </si>
   <si>
     <t>65.38%</t>
   </si>
   <si>
+    <t>69.35%</t>
+  </si>
+  <si>
     <t>Suites Segundo Nivel</t>
   </si>
   <si>
     <t>58.02%</t>
   </si>
   <si>
-    <t>59.57%</t>
+    <t>65.74%</t>
   </si>
   <si>
     <t>Tercer Nivel</t>
@@ -136,7 +136,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>97.13%</t>
+    <t>97.32%</t>
   </si>
 </sst>
 </file>
@@ -814,28 +814,28 @@
         <v>27</v>
       </c>
       <c r="B9" s="6">
-        <v>186</v>
+        <v>265</v>
       </c>
       <c r="C9" s="6">
-        <v>17</v>
-      </c>
-      <c r="D9" s="6">
-        <v>35</v>
+        <v>2</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="6">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>22</v>
+      <c r="I9" s="6">
+        <v>24</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>186</v>
+        <v>265</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>22</v>
@@ -870,28 +870,28 @@
         <v>27</v>
       </c>
       <c r="B10" s="6">
-        <v>265</v>
+        <v>186</v>
       </c>
       <c r="C10" s="6">
-        <v>2</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="D10" s="6">
+        <v>35</v>
+      </c>
+      <c r="E10" s="6">
+        <v>36</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="6">
-        <v>24</v>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -906,13 +906,13 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>265</v>
+        <v>186</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>22</v>
@@ -1047,7 +1047,7 @@
         <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1074,10 +1074,10 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>131</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
+        <v>117</v>
+      </c>
+      <c r="O13" s="6">
+        <v>12</v>
       </c>
       <c r="P13" s="6">
         <v>274</v>
@@ -1156,7 +1156,7 @@
         <v>370</v>
       </c>
       <c r="D15" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E15" s="6">
         <v>120</v>
@@ -1186,7 +1186,7 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
@@ -1206,28 +1206,28 @@
         <v>30</v>
       </c>
       <c r="B16" s="6">
-        <v>2774</v>
+        <v>1326</v>
       </c>
       <c r="C16" s="6">
-        <v>575</v>
+        <v>116</v>
       </c>
       <c r="D16" s="6">
-        <v>1156</v>
+        <v>406</v>
       </c>
       <c r="E16" s="6">
-        <v>427</v>
+        <v>188</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="6">
-        <v>184</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>22</v>
+        <v>309</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1</v>
       </c>
       <c r="I16" s="6">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>22</v>
@@ -1242,13 +1242,13 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>2774</v>
+        <v>1326</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>22</v>
@@ -1262,28 +1262,28 @@
         <v>30</v>
       </c>
       <c r="B17" s="6">
-        <v>1326</v>
+        <v>2691</v>
       </c>
       <c r="C17" s="6">
-        <v>116</v>
+        <v>665</v>
       </c>
       <c r="D17" s="6">
-        <v>406</v>
+        <v>995</v>
       </c>
       <c r="E17" s="6">
-        <v>188</v>
+        <v>698</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="6">
-        <v>309</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="I17" s="6">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>22</v>
@@ -1298,13 +1298,13 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>191</v>
+        <v>262</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>1326</v>
+        <v>2691</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>22</v>
@@ -1318,28 +1318,28 @@
         <v>30</v>
       </c>
       <c r="B18" s="6">
-        <v>2691</v>
+        <v>2774</v>
       </c>
       <c r="C18" s="6">
-        <v>662</v>
+        <v>575</v>
       </c>
       <c r="D18" s="6">
-        <v>995</v>
+        <v>1156</v>
       </c>
       <c r="E18" s="6">
-        <v>679</v>
+        <v>430</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>34</v>
+        <v>184</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="6">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>22</v>
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>284</v>
+        <v>203</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>2691</v>
+        <v>2774</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>22</v>
@@ -1374,28 +1374,28 @@
         <v>31</v>
       </c>
       <c r="B19" s="6">
-        <v>390</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>22</v>
+        <v>1900</v>
+      </c>
+      <c r="C19" s="6">
+        <v>736</v>
       </c>
       <c r="D19" s="6">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E19" s="6">
-        <v>124</v>
+        <v>326</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="6">
-        <v>43</v>
+      <c r="G19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1410,13 +1410,13 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>179</v>
+        <v>59</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>390</v>
+        <v>1900</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>22</v>
@@ -1430,28 +1430,28 @@
         <v>31</v>
       </c>
       <c r="B20" s="6">
-        <v>1900</v>
-      </c>
-      <c r="C20" s="6">
-        <v>736</v>
+        <v>390</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D20" s="6">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="E20" s="6">
-        <v>321</v>
+        <v>160</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>22</v>
+      <c r="G20" s="6">
+        <v>43</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="6">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>22</v>
@@ -1466,13 +1466,13 @@
         <v>22</v>
       </c>
       <c r="N20" s="6">
-        <v>57</v>
-      </c>
-      <c r="O20" s="6">
-        <v>7</v>
+        <v>143</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>1900</v>
+        <v>390</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>22</v>
@@ -1486,28 +1486,28 @@
         <v>32</v>
       </c>
       <c r="B21" s="6">
-        <v>336</v>
-      </c>
-      <c r="C21" s="6">
-        <v>12</v>
+        <v>216</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="6">
-        <v>28</v>
+      <c r="E21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="6">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>22</v>
@@ -1522,16 +1522,16 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>209</v>
+        <v>144</v>
       </c>
       <c r="Q21" s="6">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>33</v>
@@ -1542,7 +1542,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="6">
-        <v>216</v>
+        <v>312</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>22</v>
@@ -1550,14 +1550,14 @@
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>22</v>
+      <c r="E22" s="6">
+        <v>12</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="6">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>22</v>
@@ -1578,16 +1578,16 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="Q22" s="6">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>34</v>
@@ -1598,28 +1598,28 @@
         <v>32</v>
       </c>
       <c r="B23" s="6">
-        <v>312</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>22</v>
+        <v>336</v>
+      </c>
+      <c r="C23" s="6">
+        <v>12</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="6">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="6">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="6">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>22</v>
@@ -1634,16 +1634,16 @@
         <v>22</v>
       </c>
       <c r="N23" s="6">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="Q23" s="6">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>35</v>
@@ -1654,7 +1654,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="6">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>22</v>
@@ -1663,19 +1663,19 @@
         <v>22</v>
       </c>
       <c r="E24" s="6">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="6">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="6">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>22</v>
@@ -1690,19 +1690,19 @@
         <v>22</v>
       </c>
       <c r="N24" s="6">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P24" s="6">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="Q24" s="6">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -1710,7 +1710,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="6">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>22</v>
@@ -1719,19 +1719,19 @@
         <v>22</v>
       </c>
       <c r="E25" s="6">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="6">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I25" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>22</v>
@@ -1746,19 +1746,19 @@
         <v>22</v>
       </c>
       <c r="N25" s="6">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P25" s="6">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="Q25" s="6">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -1775,7 +1775,7 @@
         <v>22</v>
       </c>
       <c r="E26" s="6">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>22</v>
@@ -1808,10 +1808,10 @@
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="Q26" s="6">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>38</v>

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="43">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -109,25 +109,28 @@
     <t>Segundo Nivel</t>
   </si>
   <si>
+    <t>98.46%</t>
+  </si>
+  <si>
     <t>Suites Primer Nivel</t>
   </si>
   <si>
+    <t>69.35%</t>
+  </si>
+  <si>
+    <t>69.23%</t>
+  </si>
+  <si>
     <t>66.67%</t>
   </si>
   <si>
-    <t>65.38%</t>
-  </si>
-  <si>
-    <t>69.35%</t>
-  </si>
-  <si>
     <t>Suites Segundo Nivel</t>
   </si>
   <si>
-    <t>58.02%</t>
-  </si>
-  <si>
-    <t>65.74%</t>
+    <t>71.76%</t>
+  </si>
+  <si>
+    <t>66.05%</t>
   </si>
   <si>
     <t>Tercer Nivel</t>
@@ -136,7 +139,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>97.32%</t>
+    <t>97.52%</t>
   </si>
 </sst>
 </file>
@@ -649,10 +652,10 @@
         <v>4198</v>
       </c>
       <c r="C6" s="6">
-        <v>2565</v>
+        <v>2657</v>
       </c>
       <c r="D6" s="6">
-        <v>1448</v>
+        <v>1456</v>
       </c>
       <c r="E6" s="6">
         <v>85</v>
@@ -681,8 +684,8 @@
       <c r="M6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="6">
-        <v>100</v>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>22</v>
@@ -817,13 +820,13 @@
         <v>265</v>
       </c>
       <c r="C9" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -850,7 +853,7 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
@@ -870,28 +873,28 @@
         <v>27</v>
       </c>
       <c r="B10" s="6">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C10" s="6">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D10" s="6">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E10" s="6">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>22</v>
+      <c r="I10" s="6">
+        <v>15</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -906,13 +909,13 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>22</v>
@@ -926,28 +929,28 @@
         <v>27</v>
       </c>
       <c r="B11" s="6">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C11" s="6">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="D11" s="6">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E11" s="6">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6">
-        <v>15</v>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -962,13 +965,13 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>22</v>
@@ -982,28 +985,28 @@
         <v>28</v>
       </c>
       <c r="B12" s="6">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="C12" s="6">
-        <v>10</v>
-      </c>
-      <c r="D12" s="6">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>22</v>
+      <c r="G12" s="6">
+        <v>121</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>22</v>
+      <c r="I12" s="6">
+        <v>33</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1018,13 +1021,13 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>22</v>
@@ -1038,28 +1041,28 @@
         <v>28</v>
       </c>
       <c r="B13" s="6">
-        <v>274</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>22</v>
+        <v>199</v>
+      </c>
+      <c r="C13" s="6">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6">
+        <v>62</v>
       </c>
       <c r="E13" s="6">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="6">
-        <v>100</v>
+      <c r="G13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6">
-        <v>33</v>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1074,13 +1077,13 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>117</v>
-      </c>
-      <c r="O13" s="6">
-        <v>12</v>
+        <v>55</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>274</v>
+        <v>199</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>22</v>
@@ -1103,7 +1106,7 @@
         <v>45</v>
       </c>
       <c r="E14" s="6">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
@@ -1130,7 +1133,7 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
@@ -1209,13 +1212,13 @@
         <v>1326</v>
       </c>
       <c r="C16" s="6">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D16" s="6">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E16" s="6">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
@@ -1242,7 +1245,7 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>191</v>
+        <v>101</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
@@ -1265,13 +1268,13 @@
         <v>2691</v>
       </c>
       <c r="C17" s="6">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="D17" s="6">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E17" s="6">
-        <v>698</v>
+        <v>804</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
@@ -1298,7 +1301,7 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>262</v>
+        <v>146</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
@@ -1327,7 +1330,7 @@
         <v>1156</v>
       </c>
       <c r="E18" s="6">
-        <v>430</v>
+        <v>513</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
@@ -1339,7 +1342,7 @@
         <v>22</v>
       </c>
       <c r="I18" s="6">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>22</v>
@@ -1354,7 +1357,7 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>203</v>
+        <v>72</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
@@ -1374,28 +1377,28 @@
         <v>31</v>
       </c>
       <c r="B19" s="6">
-        <v>1900</v>
+        <v>390</v>
       </c>
       <c r="C19" s="6">
-        <v>736</v>
+        <v>62</v>
       </c>
       <c r="D19" s="6">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="E19" s="6">
-        <v>326</v>
+        <v>192</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>22</v>
+      <c r="G19" s="6">
+        <v>43</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="6">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1410,19 +1413,19 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>1900</v>
-      </c>
-      <c r="Q19" s="6" t="s">
-        <v>22</v>
+        <v>384</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>6</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1430,28 +1433,28 @@
         <v>31</v>
       </c>
       <c r="B20" s="6">
-        <v>390</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>22</v>
+        <v>1900</v>
+      </c>
+      <c r="C20" s="6">
+        <v>788</v>
       </c>
       <c r="D20" s="6">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E20" s="6">
-        <v>160</v>
+        <v>333</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="6">
-        <v>43</v>
+      <c r="G20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>22</v>
@@ -1465,14 +1468,14 @@
       <c r="M20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="6">
-        <v>143</v>
+      <c r="N20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>390</v>
+        <v>1900</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>22</v>
@@ -1483,31 +1486,31 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="6">
-        <v>216</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>22</v>
+        <v>336</v>
+      </c>
+      <c r="C21" s="6">
+        <v>12</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>22</v>
+      <c r="E21" s="6">
+        <v>52</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="6">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>22</v>
@@ -1522,24 +1525,24 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>144</v>
+        <v>233</v>
       </c>
       <c r="Q21" s="6">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="6">
         <v>312</v>
@@ -1551,7 +1554,7 @@
         <v>22</v>
       </c>
       <c r="E22" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>22</v>
@@ -1584,42 +1587,42 @@
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="Q22" s="6">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="6">
-        <v>336</v>
-      </c>
-      <c r="C23" s="6">
-        <v>12</v>
+        <v>216</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="6">
-        <v>52</v>
+      <c r="E23" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="6">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>22</v>
@@ -1634,36 +1637,36 @@
         <v>22</v>
       </c>
       <c r="N23" s="6">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>233</v>
+        <v>144</v>
       </c>
       <c r="Q23" s="6">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="6">
         <v>262</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>22</v>
+      <c r="C24" s="6">
+        <v>36</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E24" s="6">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>22</v>
@@ -1675,7 +1678,7 @@
         <v>22</v>
       </c>
       <c r="I24" s="6">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>22</v>
@@ -1690,24 +1693,24 @@
         <v>22</v>
       </c>
       <c r="N24" s="6">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P24" s="6">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="Q24" s="6">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" s="6">
         <v>264</v>
@@ -1758,12 +1761,12 @@
         <v>88</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6">
         <v>324</v>
@@ -1775,13 +1778,13 @@
         <v>22</v>
       </c>
       <c r="E26" s="6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="6">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>22</v>
@@ -1802,36 +1805,36 @@
         <v>22</v>
       </c>
       <c r="N26" s="6">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q26" s="6">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27" s="6">
         <v>5441</v>
       </c>
       <c r="C27" s="6">
-        <v>4248</v>
+        <v>4316</v>
       </c>
       <c r="D27" s="6">
         <v>757</v>
       </c>
       <c r="E27" s="6">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>22</v>
@@ -1858,7 +1861,7 @@
         <v>22</v>
       </c>
       <c r="N27" s="6">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>22</v>
@@ -1875,7 +1878,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B28" s="7">
         <f>SUM(B6:B27)</f>
@@ -1926,7 +1929,7 @@
         <f>SUM(Q6:Q27)</f>
       </c>
       <c r="R28" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="45">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -97,6 +97,9 @@
     <t>Palco Azul</t>
   </si>
   <si>
+    <t>97.74%</t>
+  </si>
+  <si>
     <t>Palco Rojo</t>
   </si>
   <si>
@@ -106,24 +109,27 @@
     <t>Primer Nivel</t>
   </si>
   <si>
+    <t>99.89%</t>
+  </si>
+  <si>
     <t>Segundo Nivel</t>
   </si>
   <si>
-    <t>98.46%</t>
+    <t>96.92%</t>
   </si>
   <si>
     <t>Suites Primer Nivel</t>
   </si>
   <si>
+    <t>66.67%</t>
+  </si>
+  <si>
     <t>69.35%</t>
   </si>
   <si>
     <t>69.23%</t>
   </si>
   <si>
-    <t>66.67%</t>
-  </si>
-  <si>
     <t>Suites Segundo Nivel</t>
   </si>
   <si>
@@ -139,7 +145,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>97.52%</t>
+    <t>97.45%</t>
   </si>
 </sst>
 </file>
@@ -853,19 +859,19 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>265</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>22</v>
+        <v>259</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>6</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -873,28 +879,28 @@
         <v>27</v>
       </c>
       <c r="B10" s="6">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C10" s="6">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="D10" s="6">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E10" s="6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="6">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="6">
-        <v>15</v>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>22</v>
@@ -909,13 +915,13 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>22</v>
@@ -929,28 +935,28 @@
         <v>27</v>
       </c>
       <c r="B11" s="6">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C11" s="6">
+        <v>69</v>
+      </c>
+      <c r="D11" s="6">
         <v>29</v>
       </c>
-      <c r="D11" s="6">
-        <v>35</v>
-      </c>
       <c r="E11" s="6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>22</v>
+      <c r="I11" s="6">
+        <v>15</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -965,13 +971,13 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>22</v>
@@ -982,31 +988,31 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="6">
-        <v>274</v>
+        <v>199</v>
       </c>
       <c r="C12" s="6">
-        <v>57</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>22</v>
+        <v>22</v>
+      </c>
+      <c r="D12" s="6">
+        <v>62</v>
       </c>
       <c r="E12" s="6">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="6">
-        <v>121</v>
+      <c r="G12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="6">
-        <v>33</v>
+      <c r="I12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1021,13 +1027,13 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>274</v>
+        <v>199</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>22</v>
@@ -1038,31 +1044,31 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="6">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="C13" s="6">
-        <v>22</v>
-      </c>
-      <c r="D13" s="6">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E13" s="6">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
+      <c r="G13" s="6">
+        <v>121</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
+      <c r="I13" s="6">
+        <v>33</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1077,13 +1083,13 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>22</v>
@@ -1094,7 +1100,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="6">
         <v>188</v>
@@ -1150,7 +1156,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="6">
         <v>630</v>
@@ -1206,31 +1212,31 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="6">
-        <v>1326</v>
+        <v>2774</v>
       </c>
       <c r="C16" s="6">
-        <v>122</v>
+        <v>575</v>
       </c>
       <c r="D16" s="6">
-        <v>408</v>
+        <v>1156</v>
       </c>
       <c r="E16" s="6">
-        <v>270</v>
+        <v>513</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="6">
-        <v>309</v>
-      </c>
-      <c r="H16" s="6">
-        <v>1</v>
+        <v>184</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="I16" s="6">
-        <v>115</v>
+        <v>274</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>22</v>
@@ -1245,48 +1251,48 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>1326</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>22</v>
+        <v>2771</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>3</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="6">
-        <v>2691</v>
+        <v>1326</v>
       </c>
       <c r="C17" s="6">
-        <v>674</v>
+        <v>122</v>
       </c>
       <c r="D17" s="6">
-        <v>996</v>
+        <v>408</v>
       </c>
       <c r="E17" s="6">
-        <v>804</v>
+        <v>270</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="6">
-        <v>34</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>22</v>
+        <v>309</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
       </c>
       <c r="I17" s="6">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>22</v>
@@ -1301,13 +1307,13 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>2691</v>
+        <v>1326</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>22</v>
@@ -1318,31 +1324,31 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" s="6">
-        <v>2774</v>
+        <v>2691</v>
       </c>
       <c r="C18" s="6">
-        <v>575</v>
+        <v>674</v>
       </c>
       <c r="D18" s="6">
-        <v>1156</v>
+        <v>996</v>
       </c>
       <c r="E18" s="6">
-        <v>513</v>
+        <v>804</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="6">
-        <v>274</v>
+        <v>37</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>22</v>
@@ -1357,13 +1363,13 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>2774</v>
+        <v>2691</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>22</v>
@@ -1374,7 +1380,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B19" s="6">
         <v>390</v>
@@ -1413,24 +1419,24 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="Q19" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B20" s="6">
         <v>1900</v>
@@ -1486,31 +1492,31 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B21" s="6">
-        <v>336</v>
-      </c>
-      <c r="C21" s="6">
-        <v>12</v>
+        <v>216</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="6">
-        <v>52</v>
+      <c r="E21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="6">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>22</v>
@@ -1525,48 +1531,48 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>233</v>
+        <v>144</v>
       </c>
       <c r="Q21" s="6">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B22" s="6">
-        <v>312</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>22</v>
+        <v>336</v>
+      </c>
+      <c r="C22" s="6">
+        <v>12</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E22" s="6">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="6">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="6">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>22</v>
@@ -1581,27 +1587,27 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="Q22" s="6">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B23" s="6">
-        <v>216</v>
+        <v>312</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>22</v>
@@ -1609,14 +1615,14 @@
       <c r="D23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>22</v>
+      <c r="E23" s="6">
+        <v>24</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="6">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>22</v>
@@ -1637,104 +1643,104 @@
         <v>22</v>
       </c>
       <c r="N23" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>144</v>
+        <v>216</v>
       </c>
       <c r="Q23" s="6">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="6">
-        <v>262</v>
-      </c>
-      <c r="C24" s="6">
+        <v>264</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="6">
+        <v>48</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="6">
+        <v>92</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="6">
+        <v>24</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="6">
+        <v>12</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" s="6">
+        <v>176</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>88</v>
+      </c>
+      <c r="R24" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="6">
-        <v>44</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="6">
-        <v>60</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="6">
-        <v>32</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N24" s="6">
-        <v>16</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P24" s="6">
-        <v>188</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>74</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="6">
-        <v>264</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>22</v>
+        <v>262</v>
+      </c>
+      <c r="C25" s="6">
+        <v>36</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="6">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="6">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I25" s="6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>22</v>
@@ -1749,24 +1755,24 @@
         <v>22</v>
       </c>
       <c r="N25" s="6">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P25" s="6">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="Q25" s="6">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" s="6">
         <v>324</v>
@@ -1817,12 +1823,12 @@
         <v>110</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B27" s="6">
         <v>5441</v>
@@ -1878,7 +1884,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B28" s="7">
         <f>SUM(B6:B27)</f>
@@ -1929,7 +1935,7 @@
         <f>SUM(Q6:Q27)</f>
       </c>
       <c r="R28" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -124,28 +124,28 @@
     <t>66.67%</t>
   </si>
   <si>
+    <t>69.23%</t>
+  </si>
+  <si>
     <t>69.35%</t>
   </si>
   <si>
-    <t>69.23%</t>
-  </si>
-  <si>
     <t>Suites Segundo Nivel</t>
   </si>
   <si>
+    <t>63.58%</t>
+  </si>
+  <si>
     <t>71.76%</t>
   </si>
   <si>
-    <t>66.05%</t>
-  </si>
-  <si>
     <t>Tercer Nivel</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>97.45%</t>
+    <t>97.41%</t>
   </si>
 </sst>
 </file>
@@ -991,28 +991,28 @@
         <v>29</v>
       </c>
       <c r="B12" s="6">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="C12" s="6">
-        <v>22</v>
-      </c>
-      <c r="D12" s="6">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>22</v>
+      <c r="G12" s="6">
+        <v>121</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>22</v>
+      <c r="I12" s="6">
+        <v>33</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1027,13 +1027,13 @@
         <v>22</v>
       </c>
       <c r="N12" s="6">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>22</v>
@@ -1047,28 +1047,28 @@
         <v>29</v>
       </c>
       <c r="B13" s="6">
-        <v>274</v>
+        <v>199</v>
       </c>
       <c r="C13" s="6">
-        <v>57</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>22</v>
+        <v>22</v>
+      </c>
+      <c r="D13" s="6">
+        <v>62</v>
       </c>
       <c r="E13" s="6">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="6">
-        <v>121</v>
+      <c r="G13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6">
-        <v>33</v>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1083,13 +1083,13 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>274</v>
+        <v>199</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>22</v>
@@ -1215,28 +1215,28 @@
         <v>31</v>
       </c>
       <c r="B16" s="6">
-        <v>2774</v>
+        <v>2691</v>
       </c>
       <c r="C16" s="6">
-        <v>575</v>
+        <v>674</v>
       </c>
       <c r="D16" s="6">
-        <v>1156</v>
+        <v>996</v>
       </c>
       <c r="E16" s="6">
-        <v>513</v>
+        <v>804</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="6">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="6">
-        <v>274</v>
+        <v>37</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>22</v>
@@ -1251,19 +1251,19 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>2771</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>3</v>
+        <v>2691</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -1271,28 +1271,28 @@
         <v>31</v>
       </c>
       <c r="B17" s="6">
-        <v>1326</v>
+        <v>2774</v>
       </c>
       <c r="C17" s="6">
-        <v>122</v>
+        <v>575</v>
       </c>
       <c r="D17" s="6">
-        <v>408</v>
+        <v>1156</v>
       </c>
       <c r="E17" s="6">
-        <v>270</v>
+        <v>513</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="6">
-        <v>309</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1</v>
+        <v>184</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="I17" s="6">
-        <v>115</v>
+        <v>274</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>22</v>
@@ -1307,19 +1307,19 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>1326</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>22</v>
+        <v>2771</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>3</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1327,28 +1327,28 @@
         <v>31</v>
       </c>
       <c r="B18" s="6">
-        <v>2691</v>
+        <v>1326</v>
       </c>
       <c r="C18" s="6">
-        <v>674</v>
+        <v>122</v>
       </c>
       <c r="D18" s="6">
-        <v>996</v>
+        <v>408</v>
       </c>
       <c r="E18" s="6">
-        <v>804</v>
+        <v>270</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>34</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>22</v>
+        <v>309</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1</v>
       </c>
       <c r="I18" s="6">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>22</v>
@@ -1363,13 +1363,13 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>2691</v>
+        <v>1326</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>22</v>
@@ -1383,28 +1383,28 @@
         <v>33</v>
       </c>
       <c r="B19" s="6">
-        <v>390</v>
+        <v>1900</v>
       </c>
       <c r="C19" s="6">
-        <v>62</v>
+        <v>788</v>
       </c>
       <c r="D19" s="6">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E19" s="6">
-        <v>192</v>
+        <v>333</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="6">
-        <v>43</v>
+      <c r="G19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1418,20 +1418,20 @@
       <c r="M19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="6">
-        <v>37</v>
+      <c r="N19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>378</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>12</v>
+        <v>1900</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1439,28 +1439,28 @@
         <v>33</v>
       </c>
       <c r="B20" s="6">
-        <v>1900</v>
+        <v>390</v>
       </c>
       <c r="C20" s="6">
-        <v>788</v>
+        <v>62</v>
       </c>
       <c r="D20" s="6">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="E20" s="6">
-        <v>333</v>
+        <v>192</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>22</v>
+      <c r="G20" s="6">
+        <v>43</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="6">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>22</v>
@@ -1474,20 +1474,20 @@
       <c r="M20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="6" t="s">
-        <v>22</v>
+      <c r="N20" s="6">
+        <v>37</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>1900</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>22</v>
+        <v>378</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>12</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -1551,28 +1551,28 @@
         <v>35</v>
       </c>
       <c r="B22" s="6">
-        <v>336</v>
-      </c>
-      <c r="C22" s="6">
-        <v>12</v>
+        <v>312</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E22" s="6">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="6">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>22</v>
@@ -1587,16 +1587,16 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="Q22" s="6">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>37</v>
@@ -1607,28 +1607,28 @@
         <v>35</v>
       </c>
       <c r="B23" s="6">
-        <v>312</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>22</v>
+        <v>336</v>
+      </c>
+      <c r="C23" s="6">
+        <v>12</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="6">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="6">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="6">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>22</v>
@@ -1643,16 +1643,16 @@
         <v>22</v>
       </c>
       <c r="N23" s="6">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="Q23" s="6">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>38</v>
@@ -1719,28 +1719,28 @@
         <v>39</v>
       </c>
       <c r="B25" s="6">
-        <v>262</v>
-      </c>
-      <c r="C25" s="6">
-        <v>36</v>
+        <v>324</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="6">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I25" s="6">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>22</v>
@@ -1755,16 +1755,16 @@
         <v>22</v>
       </c>
       <c r="N25" s="6">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P25" s="6">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="Q25" s="6">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>40</v>
@@ -1775,28 +1775,28 @@
         <v>39</v>
       </c>
       <c r="B26" s="6">
-        <v>324</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>22</v>
+        <v>262</v>
+      </c>
+      <c r="C26" s="6">
+        <v>36</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E26" s="6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="6">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I26" s="6">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>22</v>
@@ -1811,16 +1811,16 @@
         <v>22</v>
       </c>
       <c r="N26" s="6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="Q26" s="6">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>41</v>

--- a/data/asistencia/Sultanes 2026.xlsx
+++ b/data/asistencia/Sultanes 2026.xlsx
@@ -121,22 +121,22 @@
     <t>Suites Primer Nivel</t>
   </si>
   <si>
+    <t>69.35%</t>
+  </si>
+  <si>
+    <t>69.23%</t>
+  </si>
+  <si>
     <t>66.67%</t>
   </si>
   <si>
-    <t>69.23%</t>
-  </si>
-  <si>
-    <t>69.35%</t>
-  </si>
-  <si>
     <t>Suites Segundo Nivel</t>
   </si>
   <si>
+    <t>71.76%</t>
+  </si>
+  <si>
     <t>63.58%</t>
-  </si>
-  <si>
-    <t>71.76%</t>
   </si>
   <si>
     <t>Tercer Nivel</t>
@@ -1271,28 +1271,28 @@
         <v>31</v>
       </c>
       <c r="B17" s="6">
-        <v>2774</v>
+        <v>1326</v>
       </c>
       <c r="C17" s="6">
-        <v>575</v>
+        <v>122</v>
       </c>
       <c r="D17" s="6">
-        <v>1156</v>
+        <v>408</v>
       </c>
       <c r="E17" s="6">
-        <v>513</v>
+        <v>270</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="6">
-        <v>184</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>22</v>
+        <v>309</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
       </c>
       <c r="I17" s="6">
-        <v>274</v>
+        <v>115</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>22</v>
@@ -1307,19 +1307,19 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>2771</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>3</v>
+        <v>1326</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1327,28 +1327,28 @@
         <v>31</v>
       </c>
       <c r="B18" s="6">
-        <v>1326</v>
+        <v>2774</v>
       </c>
       <c r="C18" s="6">
-        <v>122</v>
+        <v>575</v>
       </c>
       <c r="D18" s="6">
-        <v>408</v>
+        <v>1156</v>
       </c>
       <c r="E18" s="6">
-        <v>270</v>
+        <v>513</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="6">
-        <v>309</v>
-      </c>
-      <c r="H18" s="6">
-        <v>1</v>
+        <v>184</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="I18" s="6">
-        <v>115</v>
+        <v>274</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>22</v>
@@ -1363,19 +1363,19 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>1326</v>
-      </c>
-      <c r="Q18" s="6" t="s">
-        <v>22</v>
+        <v>2771</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>3</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -1383,28 +1383,28 @@
         <v>33</v>
       </c>
       <c r="B19" s="6">
-        <v>1900</v>
+        <v>390</v>
       </c>
       <c r="C19" s="6">
-        <v>788</v>
+        <v>62</v>
       </c>
       <c r="D19" s="6">
-        <v>778</v>
+        <v>16</v>
       </c>
       <c r="E19" s="6">
-        <v>333</v>
+        <v>192</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>22</v>
+      <c r="G19" s="6">
+        <v>43</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="6">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1418,20 +1418,20 @@
       <c r="M19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="6" t="s">
-        <v>22</v>
+      <c r="N19" s="6">
+        <v>37</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>1900</v>
-      </c>
-      <c r="Q19" s="6" t="s">
-        <v>22</v>
+        <v>378</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>12</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1439,28 +1439,28 @@
         <v>33</v>
       </c>
       <c r="B20" s="6">
-        <v>390</v>
+        <v>1900</v>
       </c>
       <c r="C20" s="6">
-        <v>62</v>
+        <v>788</v>
       </c>
       <c r="D20" s="6">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="E20" s="6">
-        <v>192</v>
+        <v>333</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="6">
-        <v>43</v>
+      <c r="G20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>22</v>
@@ -1474,20 +1474,20 @@
       <c r="M20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="6">
-        <v>37</v>
+      <c r="N20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>378</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>12</v>
+        <v>1900</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -1495,28 +1495,28 @@
         <v>35</v>
       </c>
       <c r="B21" s="6">
-        <v>216</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>22</v>
+        <v>336</v>
+      </c>
+      <c r="C21" s="6">
+        <v>12</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>22</v>
+      <c r="E21" s="6">
+        <v>52</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="6">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="6">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>22</v>
@@ -1531,16 +1531,16 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>144</v>
+        <v>233</v>
       </c>
       <c r="Q21" s="6">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>36</v>
@@ -1607,28 +1607,28 @@
         <v>35</v>
       </c>
       <c r="B23" s="6">
-        <v>336</v>
-      </c>
-      <c r="C23" s="6">
-        <v>12</v>
+        <v>216</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="6">
-        <v>52</v>
+      <c r="E23" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="6">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>22</v>
@@ -1643,16 +1643,16 @@
         <v>22</v>
       </c>
       <c r="N23" s="6">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>233</v>
+        <v>144</v>
       </c>
       <c r="Q23" s="6">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>38</v>
@@ -1663,28 +1663,28 @@
         <v>39</v>
       </c>
       <c r="B24" s="6">
-        <v>264</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>22</v>
+        <v>262</v>
+      </c>
+      <c r="C24" s="6">
+        <v>36</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E24" s="6">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="6">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>22</v>
@@ -1699,19 +1699,19 @@
         <v>22</v>
       </c>
       <c r="N24" s="6">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P24" s="6">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="Q24" s="6">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -1767,7 +1767,7 @@
         <v>118</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -1775,28 +1775,28 @@
         <v>39</v>
       </c>
       <c r="B26" s="6">
-        <v>262</v>
-      </c>
-      <c r="C26" s="6">
-        <v>36</v>
+        <v>264</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E26" s="6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="6">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I26" s="6">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>22</v>
@@ -1811,19 +1811,19 @@
         <v>22</v>
       </c>
       <c r="N26" s="6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P26" s="6">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="Q26" s="6">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
